--- a/Ciclo 02 - 2026/Cuadro de notas.xlsx
+++ b/Ciclo 02 - 2026/Cuadro de notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 02 - 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 02 - 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C6C62D0-9038-4DCB-9275-765AD9BF26DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B3F343-CEA9-4C18-B962-4DE3278DAE8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>Analisis Financiero</t>
   </si>
@@ -52,6 +49,90 @@
   </si>
   <si>
     <t>Comunicaciones 1</t>
+  </si>
+  <si>
+    <t>Laboratorio 1 Asincronico</t>
+  </si>
+  <si>
+    <t>Parcial 1</t>
+  </si>
+  <si>
+    <t>Laboratorio 2 Sincronico mas Guias</t>
+  </si>
+  <si>
+    <t>Parcial 2</t>
+  </si>
+  <si>
+    <t>Proyecto</t>
+  </si>
+  <si>
+    <t>Laboratorio 3 Sincronico mas Guias</t>
+  </si>
+  <si>
+    <t>Trabajo Grupal Etapa 1</t>
+  </si>
+  <si>
+    <t>Investigacion Documental</t>
+  </si>
+  <si>
+    <t>Ensayo</t>
+  </si>
+  <si>
+    <t>Trabajo Grupal Etapa 2</t>
+  </si>
+  <si>
+    <t>Laboratorio Practico 1 Asinc</t>
+  </si>
+  <si>
+    <t>Curso Huawei Asinc</t>
+  </si>
+  <si>
+    <t>Laboratorio Practico 2 Asinc</t>
+  </si>
+  <si>
+    <t>Laboratorio Practico 3 Asinc</t>
+  </si>
+  <si>
+    <t>Laboratorio Practico 4 Asinc</t>
+  </si>
+  <si>
+    <t>Proyecto de Catedra</t>
+  </si>
+  <si>
+    <t>Practica de Laboratorio 1</t>
+  </si>
+  <si>
+    <t>Practica de Laboratorio 2</t>
+  </si>
+  <si>
+    <t>Practica de Laboratorio 3</t>
+  </si>
+  <si>
+    <t>Proyecto Entregable 1</t>
+  </si>
+  <si>
+    <t>Proyecto Entregable 2</t>
+  </si>
+  <si>
+    <t>Exposicion Proyecto</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Desafio Practico 1</t>
+  </si>
+  <si>
+    <t>Desafio Practico 2</t>
+  </si>
+  <si>
+    <t>Desafio Practico 3</t>
+  </si>
+  <si>
+    <t>Desafio Practico 4</t>
+  </si>
+  <si>
+    <t>Curso Huawei</t>
   </si>
 </sst>
 </file>
@@ -127,14 +208,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
@@ -145,6 +218,13 @@
       <b/>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -194,7 +274,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -313,7 +393,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -329,7 +409,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="medium">
@@ -342,13 +422,45 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -356,44 +468,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -444,6 +531,61 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -760,7 +902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A82A0CD-7BCC-4D99-8D34-01F85165CA32}">
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
@@ -770,275 +912,530 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="39"/>
-      <c r="F2" s="40" t="s">
+      <c r="A2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="22"/>
+      <c r="F2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="42"/>
-      <c r="K2" s="43" t="s">
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="25"/>
+      <c r="K2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="45"/>
-    </row>
-    <row r="3" spans="1:14" s="3" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="13"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="7"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="7"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="28"/>
+    </row>
+    <row r="3" spans="1:14" s="2" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="38">
+        <v>0.2</v>
+      </c>
+      <c r="C3" s="53">
+        <v>7.5</v>
+      </c>
+      <c r="D3" s="6">
+        <f>+C3*B3</f>
+        <v>1.5</v>
+      </c>
+      <c r="F3" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="54">
+        <v>0.1</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="4">
+        <f>+G3*H3</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" s="36">
+        <v>0.1</v>
+      </c>
+      <c r="M3" s="3">
+        <v>10</v>
+      </c>
+      <c r="N3" s="4">
+        <f>+L3*M3</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="17"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="24"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="8"/>
+      <c r="A4" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="54">
+        <v>0.1</v>
+      </c>
+      <c r="C4" s="5">
+        <v>8.14</v>
+      </c>
+      <c r="D4" s="6">
+        <f t="shared" ref="D4:D8" si="0">+C4*B4</f>
+        <v>0.81400000000000006</v>
+      </c>
+      <c r="F4" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="54">
+        <v>0.15</v>
+      </c>
+      <c r="H4" s="5"/>
+      <c r="I4" s="4">
+        <f t="shared" ref="I4:I9" si="1">+G4*H4</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="L4" s="36">
+        <v>0.15</v>
+      </c>
+      <c r="M4" s="10">
+        <v>7.15</v>
+      </c>
+      <c r="N4" s="4">
+        <f t="shared" ref="N4:N10" si="2">+L4*M4</f>
+        <v>1.0725</v>
+      </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="17"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="24"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="8"/>
+      <c r="A5" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="32">
+        <v>0.2</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F5" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="43">
+        <v>0.15</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="I5" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="44" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="45">
+        <v>0.1</v>
+      </c>
+      <c r="M5" s="10"/>
+      <c r="N5" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="17"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="24"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="8"/>
+      <c r="A6" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="32">
+        <v>0.1</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F6" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="45">
+        <v>0.2</v>
+      </c>
+      <c r="H6" s="5"/>
+      <c r="I6" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="L6" s="55">
+        <v>0.1</v>
+      </c>
+      <c r="M6" s="10"/>
+      <c r="N6" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="24"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="8"/>
+      <c r="A7" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="34">
+        <v>0.2</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F7" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="43">
+        <v>0.2</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="I7" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K7" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7" s="43">
+        <v>0.1</v>
+      </c>
+      <c r="M7" s="10"/>
+      <c r="N7" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="19"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="24"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="26"/>
-      <c r="I8" s="8"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="8"/>
+      <c r="A8" s="33" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="34">
+        <v>0.2</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F8" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="43">
+        <v>0.2</v>
+      </c>
+      <c r="H8" s="11"/>
+      <c r="I8" s="4">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="47">
+        <v>0.15</v>
+      </c>
+      <c r="M8" s="10"/>
+      <c r="N8" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="19"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="24"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="8"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="29"/>
-    </row>
-    <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="16"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="13"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="8"/>
-    </row>
-    <row r="11" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="24"/>
-      <c r="G11" s="21"/>
-      <c r="I11" s="29"/>
-    </row>
-    <row r="12" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="19"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="24"/>
-    </row>
-    <row r="13" spans="1:14" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B13" s="21"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="23"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-    </row>
-    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
+      <c r="B9" s="9">
+        <f>SUM(B3:B8)</f>
+        <v>1</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="12">
+        <f>SUM(D3:D8)</f>
+        <v>2.3140000000000001</v>
+      </c>
+      <c r="F9" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="11"/>
+      <c r="I9" s="4"/>
+      <c r="K9" s="42" t="s">
+        <v>20</v>
+      </c>
+      <c r="L9" s="43">
+        <v>0.2</v>
+      </c>
+      <c r="M9" s="7"/>
+      <c r="N9" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="G10" s="9">
+        <f>SUM(G3:G9)</f>
+        <v>1</v>
+      </c>
+      <c r="I10" s="12"/>
+      <c r="K10" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="L10" s="49">
+        <v>0.1</v>
+      </c>
+      <c r="N10" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="L11" s="1">
+        <f>SUM(L3:L10)</f>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="N11" s="12">
+        <f>SUM(N3:N10)</f>
+        <v>2.0724999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="33"/>
-      <c r="F17" s="34" t="s">
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="16"/>
+    </row>
+    <row r="14" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="40">
+        <v>0.2</v>
+      </c>
+      <c r="C14" s="3">
+        <v>10</v>
+      </c>
+      <c r="D14" s="4">
+        <f>+B14*C14</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="30">
+        <v>0.15</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="4">
+        <f t="shared" ref="D15:D18" si="3">+B15*C15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="30">
+        <v>0.3</v>
+      </c>
+      <c r="C16" s="5"/>
+      <c r="D16" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G17" s="35"/>
-      <c r="H17" s="35"/>
-      <c r="I17" s="36"/>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="7"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="7"/>
-    </row>
-    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="19"/>
-      <c r="B19" s="20"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="19"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+    </row>
+    <row r="17" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="30">
+        <v>0.15</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="G17" s="38">
+        <v>0.1</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" ref="I17:I18" si="4">+G17*H17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="32">
+        <v>0.2</v>
+      </c>
+      <c r="C18" s="13"/>
+      <c r="D18" s="4">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="39" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="40">
+        <v>0.1</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="7"/>
+      <c r="B19" s="9">
+        <f>SUM(B14:B18)</f>
+        <v>1</v>
+      </c>
       <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-    </row>
-    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-    </row>
-    <row r="21" spans="1:14" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="19"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="8"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
+      <c r="D19" s="12">
+        <f>SUM(D14:D18)</f>
+        <v>2</v>
+      </c>
+      <c r="F19" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="38">
+        <v>0.15</v>
+      </c>
+      <c r="H19" s="5">
+        <v>8.9</v>
+      </c>
+      <c r="I19" s="5">
+        <f>+G19*H19</f>
+        <v>1.335</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F20" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="40">
+        <v>0.1</v>
+      </c>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5">
+        <f t="shared" ref="I20:I24" si="5">+G20*H20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" s="2" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="F21" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" s="32">
+        <v>0.1</v>
+      </c>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="K21"/>
       <c r="L21"/>
       <c r="M21"/>
       <c r="N21"/>
     </row>
-    <row r="22" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="19"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="8"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
+    <row r="22" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F22" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="32">
+        <v>0.1</v>
+      </c>
+      <c r="H22" s="11"/>
+      <c r="I22" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="19"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="8"/>
+      <c r="F23" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="32">
+        <v>0.15</v>
+      </c>
+      <c r="H23" s="11"/>
+      <c r="I23" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="19"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="8"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="26"/>
-      <c r="I24" s="8"/>
+      <c r="F24" s="51" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="52">
+        <v>0.2</v>
+      </c>
+      <c r="H24" s="11"/>
+      <c r="I24" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="14"/>
-      <c r="B25" s="21"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="2"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="8"/>
-    </row>
-    <row r="26" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G26" s="21"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="29"/>
+      <c r="G25" s="9">
+        <f>SUM(G17:G24)</f>
+        <v>1</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="12">
+        <f>SUM(I17:I24)</f>
+        <v>1.335</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="F16:I16"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="F2:I2"/>
     <mergeCell ref="K2:N2"/>

--- a/Ciclo 02 - 2026/Cuadro de notas.xlsx
+++ b/Ciclo 02 - 2026/Cuadro de notas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 02 - 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B3F343-CEA9-4C18-B962-4DE3278DAE8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{806D056C-965C-4AF9-B058-375DCD0C9EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
   <si>
     <t>Analisis Financiero</t>
   </si>
@@ -112,12 +112,6 @@
   </si>
   <si>
     <t>Proyecto Entregable 2</t>
-  </si>
-  <si>
-    <t>Exposicion Proyecto</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>Desafio Practico 1</t>
@@ -468,7 +462,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -487,96 +481,48 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -584,9 +530,52 @@
     <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -902,7 +891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A82A0CD-7BCC-4D99-8D34-01F85165CA32}">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
@@ -912,43 +901,43 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="22"/>
-      <c r="F2" s="23" t="s">
+      <c r="A2" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="47"/>
+      <c r="F2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="25"/>
-      <c r="K2" s="26" t="s">
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="50"/>
+      <c r="K2" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="28"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="53"/>
     </row>
     <row r="3" spans="1:14" s="2" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="38">
+      <c r="B3" s="23">
         <v>0.2</v>
       </c>
-      <c r="C3" s="53">
+      <c r="C3" s="37">
         <v>7.5</v>
       </c>
       <c r="D3" s="6">
         <f>+C3*B3</f>
         <v>1.5</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="54">
+      <c r="G3" s="38">
         <v>0.1</v>
       </c>
       <c r="H3" s="3"/>
@@ -956,10 +945,10 @@
         <f>+G3*H3</f>
         <v>0</v>
       </c>
-      <c r="K3" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="36">
+      <c r="K3" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="21">
         <v>0.1</v>
       </c>
       <c r="M3" s="3">
@@ -971,10 +960,10 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="54">
+      <c r="B4" s="38">
         <v>0.1</v>
       </c>
       <c r="C4" s="5">
@@ -984,21 +973,21 @@
         <f t="shared" ref="D4:D8" si="0">+C4*B4</f>
         <v>0.81400000000000006</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="54">
+      <c r="G4" s="38">
         <v>0.15</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="4">
-        <f t="shared" ref="I4:I9" si="1">+G4*H4</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="35" t="s">
+        <f t="shared" ref="I4:I8" si="1">+G4*H4</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="21">
         <v>0.15</v>
       </c>
       <c r="M4" s="10">
@@ -1010,45 +999,49 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="32">
+      <c r="B5" s="23">
         <v>0.2</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="6">
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="43">
+      <c r="G5" s="21">
         <v>0.15</v>
       </c>
       <c r="H5" s="5"/>
-      <c r="I5" s="4">
+      <c r="I5" s="54">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K5" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="45">
+      <c r="K5" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="23">
         <v>0.1</v>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="4">
+      <c r="M5" s="10">
+        <v>9</v>
+      </c>
+      <c r="N5" s="54">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="32">
+      <c r="B6" s="17">
         <v>0.1</v>
       </c>
       <c r="C6" s="5"/>
@@ -1056,10 +1049,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="45">
+      <c r="G6" s="30">
         <v>0.2</v>
       </c>
       <c r="H6" s="5"/>
@@ -1067,10 +1060,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K6" s="42" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6" s="55">
+      <c r="K6" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" s="28">
         <v>0.1</v>
       </c>
       <c r="M6" s="10"/>
@@ -1080,10 +1073,10 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="19">
         <v>0.2</v>
       </c>
       <c r="C7" s="5"/>
@@ -1091,10 +1084,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F7" s="42" t="s">
+      <c r="F7" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="43">
+      <c r="G7" s="28">
         <v>0.2</v>
       </c>
       <c r="H7" s="5"/>
@@ -1102,10 +1095,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K7" s="42" t="s">
-        <v>31</v>
-      </c>
-      <c r="L7" s="43">
+      <c r="K7" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" s="28">
         <v>0.1</v>
       </c>
       <c r="M7" s="10"/>
@@ -1115,10 +1108,10 @@
       </c>
     </row>
     <row r="8" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="34">
+      <c r="B8" s="19">
         <v>0.2</v>
       </c>
       <c r="C8" s="5"/>
@@ -1126,10 +1119,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F8" s="42" t="s">
+      <c r="F8" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="43">
+      <c r="G8" s="28">
         <v>0.2</v>
       </c>
       <c r="H8" s="11"/>
@@ -1137,10 +1130,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K8" s="46" t="s">
+      <c r="K8" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="47">
+      <c r="L8" s="32">
         <v>0.15</v>
       </c>
       <c r="M8" s="10"/>
@@ -1159,18 +1152,15 @@
         <f>SUM(D3:D8)</f>
         <v>2.3140000000000001</v>
       </c>
-      <c r="F9" s="48" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="4"/>
-      <c r="K9" s="42" t="s">
+      <c r="G9" s="9">
+        <f>SUM(G3:G8)</f>
+        <v>1</v>
+      </c>
+      <c r="I9" s="12"/>
+      <c r="K9" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="L9" s="43">
+      <c r="L9" s="28">
         <v>0.2</v>
       </c>
       <c r="M9" s="7"/>
@@ -1179,18 +1169,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="G10" s="9">
-        <f>SUM(G3:G9)</f>
-        <v>1</v>
-      </c>
-      <c r="I10" s="12"/>
-      <c r="K10" s="48" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" s="49">
+      <c r="K10" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" s="34">
         <v>0.1</v>
       </c>
       <c r="N10" s="4">
@@ -1207,235 +1192,228 @@
       </c>
       <c r="N11" s="12">
         <f>SUM(N3:N10)</f>
-        <v>2.0724999999999998</v>
+        <v>2.9724999999999997</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
+      <c r="A12" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="16"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="41"/>
+      <c r="F12" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="44"/>
+    </row>
+    <row r="13" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25">
+        <v>0.2</v>
+      </c>
+      <c r="C13" s="3">
+        <v>10</v>
+      </c>
+      <c r="D13" s="4">
+        <f>+B13*C13</f>
+        <v>2</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="23">
+        <v>0.1</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" ref="I13:I14" si="3">+G13*H13</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="39" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="40">
-        <v>0.2</v>
-      </c>
-      <c r="C14" s="3">
-        <v>10</v>
-      </c>
-      <c r="D14" s="4">
-        <f>+B14*C14</f>
-        <v>2</v>
+      <c r="A14" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="21">
+        <v>0.15</v>
+      </c>
+      <c r="C14" s="5"/>
+      <c r="D14" s="54">
+        <f t="shared" ref="D14:D17" si="4">+B14*C14</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="25">
+        <v>0.1</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="30">
+      <c r="A15" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="21">
+        <v>0.3</v>
+      </c>
+      <c r="C15" s="5">
+        <v>8.33</v>
+      </c>
+      <c r="D15" s="54">
+        <f t="shared" si="4"/>
+        <v>2.4990000000000001</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" s="23">
         <v>0.15</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="4">
-        <f t="shared" ref="D15:D18" si="3">+B15*C15</f>
-        <v>0</v>
+      <c r="H15" s="5">
+        <v>8.9</v>
+      </c>
+      <c r="I15" s="5">
+        <f>+G15*H15</f>
+        <v>1.335</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="30">
-        <v>0.3</v>
-      </c>
-      <c r="C16" s="5"/>
+      <c r="A16" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="15">
+        <v>0.15</v>
+      </c>
+      <c r="C16" s="10"/>
       <c r="D16" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="19"/>
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="25">
+        <v>0.1</v>
+      </c>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5">
+        <f t="shared" ref="I16:I20" si="5">+G16*H16</f>
+        <v>0</v>
+      </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
     </row>
     <row r="17" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="29" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="30">
+      <c r="A17" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="C17" s="13"/>
+      <c r="D17" s="4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="7"/>
+      <c r="B18" s="9">
+        <f>SUM(B13:B17)</f>
+        <v>1</v>
+      </c>
+      <c r="C18" s="8"/>
+      <c r="D18" s="12">
+        <f>SUM(D13:D17)</f>
+        <v>4.4990000000000006</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="H18" s="11"/>
+      <c r="I18" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F19" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="17">
         <v>0.15</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F17" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="38">
-        <v>0.1</v>
-      </c>
-      <c r="H17" s="3">
-        <v>0</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" ref="I17:I18" si="4">+G17*H17</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="32">
+      <c r="H19" s="11"/>
+      <c r="I19" s="5">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="F20" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="36">
         <v>0.2</v>
       </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="4">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="F18" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="G18" s="40">
-        <v>0.1</v>
-      </c>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="7"/>
-      <c r="B19" s="9">
-        <f>SUM(B14:B18)</f>
-        <v>1</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="12">
-        <f>SUM(D14:D18)</f>
-        <v>2</v>
-      </c>
-      <c r="F19" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="G19" s="38">
-        <v>0.15</v>
-      </c>
-      <c r="H19" s="5">
-        <v>8.9</v>
-      </c>
-      <c r="I19" s="5">
-        <f>+G19*H19</f>
-        <v>1.335</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F20" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" s="40">
-        <v>0.1</v>
-      </c>
-      <c r="H20" s="5"/>
+      <c r="H20" s="11"/>
       <c r="I20" s="5">
-        <f t="shared" ref="I20:I24" si="5">+G20*H20</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" s="2" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" s="2" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21"/>
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
-      <c r="F21" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="G21" s="32">
-        <v>0.1</v>
-      </c>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
+      <c r="F21"/>
+      <c r="G21" s="9">
+        <f>SUM(G13:G20)</f>
+        <v>1</v>
+      </c>
+      <c r="H21" s="1"/>
+      <c r="I21" s="12">
+        <f>SUM(I13:I20)</f>
+        <v>1.335</v>
       </c>
       <c r="K21"/>
       <c r="L21"/>
       <c r="M21"/>
       <c r="N21"/>
     </row>
-    <row r="22" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F22" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="G22" s="32">
-        <v>0.1</v>
-      </c>
-      <c r="H22" s="11"/>
-      <c r="I22" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="F23" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="G23" s="32">
-        <v>0.15</v>
-      </c>
-      <c r="H23" s="11"/>
-      <c r="I23" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="F24" s="51" t="s">
-        <v>20</v>
-      </c>
-      <c r="G24" s="52">
-        <v>0.2</v>
-      </c>
-      <c r="H24" s="11"/>
-      <c r="I24" s="5">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G25" s="9">
-        <f>SUM(G17:G24)</f>
-        <v>1</v>
-      </c>
-      <c r="H25" s="1"/>
-      <c r="I25" s="12">
-        <f>SUM(I17:I24)</f>
-        <v>1.335</v>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="F12:I12"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="F2:I2"/>
     <mergeCell ref="K2:N2"/>

--- a/Ciclo 02 - 2026/Cuadro de notas.xlsx
+++ b/Ciclo 02 - 2026/Cuadro de notas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 02 - 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{806D056C-965C-4AF9-B058-375DCD0C9EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46FD267F-17D8-4C33-8E39-974C4072CEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
@@ -268,7 +268,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -443,7 +443,91 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -452,7 +536,37 @@
       <top style="thin">
         <color theme="4" tint="0.39997558519241921"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -462,7 +576,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -478,58 +592,38 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -575,7 +669,41 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -901,54 +1029,56 @@
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="47"/>
-      <c r="F2" s="48" t="s">
+      <c r="A2" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="33"/>
+      <c r="F2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="50"/>
-      <c r="K2" s="51" t="s">
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="36"/>
+      <c r="K2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="53"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="39"/>
     </row>
     <row r="3" spans="1:14" s="2" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="17">
         <v>0.2</v>
       </c>
-      <c r="C3" s="37">
+      <c r="C3" s="22">
         <v>7.5</v>
       </c>
       <c r="D3" s="6">
         <f>+C3*B3</f>
         <v>1.5</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="38">
+      <c r="G3" s="17">
         <v>0.1</v>
       </c>
-      <c r="H3" s="3"/>
+      <c r="H3" s="3">
+        <v>10</v>
+      </c>
       <c r="I3" s="4">
         <f>+G3*H3</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="21">
+      <c r="L3" s="18">
         <v>0.1</v>
       </c>
       <c r="M3" s="3">
@@ -960,10 +1090,10 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="38">
+      <c r="B4" s="23">
         <v>0.1</v>
       </c>
       <c r="C4" s="5">
@@ -973,21 +1103,23 @@
         <f t="shared" ref="D4:D8" si="0">+C4*B4</f>
         <v>0.81400000000000006</v>
       </c>
-      <c r="F4" s="26" t="s">
+      <c r="F4" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="38">
+      <c r="G4" s="23">
         <v>0.15</v>
       </c>
-      <c r="H4" s="5"/>
+      <c r="H4" s="5">
+        <v>7.6</v>
+      </c>
       <c r="I4" s="4">
         <f t="shared" ref="I4:I8" si="1">+G4*H4</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="20" t="s">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="K4" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="L4" s="21">
+      <c r="L4" s="16">
         <v>0.15</v>
       </c>
       <c r="M4" s="10">
@@ -999,49 +1131,51 @@
       </c>
     </row>
     <row r="5" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="17">
         <v>0.2</v>
       </c>
       <c r="C5" s="5">
         <v>0</v>
       </c>
-      <c r="D5" s="54">
+      <c r="D5" s="24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="16">
         <v>0.15</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="54">
+      <c r="H5" s="5">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I5" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="22" t="s">
+        <v>1.47</v>
+      </c>
+      <c r="K5" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="L5" s="23">
+      <c r="L5" s="17">
         <v>0.1</v>
       </c>
       <c r="M5" s="10">
         <v>9</v>
       </c>
-      <c r="N5" s="54">
+      <c r="N5" s="24">
         <f t="shared" si="2"/>
         <v>0.9</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="14">
         <v>0.1</v>
       </c>
       <c r="C6" s="5"/>
@@ -1049,10 +1183,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="20">
         <v>0.2</v>
       </c>
       <c r="H6" s="5"/>
@@ -1060,10 +1194,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K6" s="27" t="s">
+      <c r="K6" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="L6" s="28">
+      <c r="L6" s="19">
         <v>0.1</v>
       </c>
       <c r="M6" s="10"/>
@@ -1073,10 +1207,10 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="15">
         <v>0.2</v>
       </c>
       <c r="C7" s="5"/>
@@ -1084,10 +1218,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F7" s="27" t="s">
+      <c r="F7" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="19">
         <v>0.2</v>
       </c>
       <c r="H7" s="5"/>
@@ -1095,10 +1229,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K7" s="27" t="s">
+      <c r="K7" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="L7" s="28">
+      <c r="L7" s="19">
         <v>0.1</v>
       </c>
       <c r="M7" s="10"/>
@@ -1108,32 +1242,32 @@
       </c>
     </row>
     <row r="8" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="13">
         <v>0.2</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="6">
+      <c r="C8" s="45"/>
+      <c r="D8" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F8" s="27" t="s">
+      <c r="F8" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="19">
         <v>0.2</v>
       </c>
-      <c r="H8" s="11"/>
-      <c r="I8" s="4">
+      <c r="H8" s="50"/>
+      <c r="I8" s="51">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K8" s="31" t="s">
+      <c r="K8" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="32">
+      <c r="L8" s="21">
         <v>0.15</v>
       </c>
       <c r="M8" s="10"/>
@@ -1156,29 +1290,33 @@
         <f>SUM(G3:G8)</f>
         <v>1</v>
       </c>
-      <c r="I9" s="12"/>
-      <c r="K9" s="27" t="s">
+      <c r="I9" s="12">
+        <f>SUM(I3:I8)</f>
+        <v>3.6099999999999994</v>
+      </c>
+      <c r="K9" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="L9" s="28">
+      <c r="L9" s="19">
         <v>0.2</v>
       </c>
-      <c r="M9" s="7"/>
+      <c r="M9" s="54"/>
       <c r="N9" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="K10" s="33" t="s">
+      <c r="K10" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="L10" s="34">
+      <c r="L10" s="55">
         <v>0.1</v>
       </c>
-      <c r="N10" s="4">
+      <c r="M10" s="56"/>
+      <c r="N10" s="51">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -1196,24 +1334,24 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="41"/>
-      <c r="F12" s="42" t="s">
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="27"/>
+      <c r="F12" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="44"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="30"/>
     </row>
     <row r="13" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="18">
         <v>0.2</v>
       </c>
       <c r="C13" s="3">
@@ -1223,77 +1361,77 @@
         <f>+B13*C13</f>
         <v>2</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="17">
         <v>0.1</v>
       </c>
       <c r="H13" s="3">
-        <v>0</v>
-      </c>
-      <c r="I13" s="5">
+        <v>8.6</v>
+      </c>
+      <c r="I13" s="60">
         <f t="shared" ref="I13:I14" si="3">+G13*H13</f>
-        <v>0</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="16">
         <v>0.15</v>
       </c>
       <c r="C14" s="5"/>
-      <c r="D14" s="54">
+      <c r="D14" s="24">
         <f t="shared" ref="D14:D17" si="4">+B14*C14</f>
         <v>0</v>
       </c>
-      <c r="F14" s="24" t="s">
+      <c r="F14" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="18">
         <v>0.1</v>
       </c>
       <c r="H14" s="5"/>
-      <c r="I14" s="5">
+      <c r="I14" s="61">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="16">
         <v>0.3</v>
       </c>
       <c r="C15" s="5">
         <v>8.33</v>
       </c>
-      <c r="D15" s="54">
+      <c r="D15" s="24">
         <f t="shared" si="4"/>
         <v>2.4990000000000001</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="17">
         <v>0.15</v>
       </c>
       <c r="H15" s="5">
-        <v>8.9</v>
-      </c>
-      <c r="I15" s="5">
+        <v>9.23</v>
+      </c>
+      <c r="I15" s="61">
         <f>+G15*H15</f>
-        <v>1.335</v>
+        <v>1.3845000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="13">
         <v>0.15</v>
       </c>
       <c r="C16" s="10"/>
@@ -1301,14 +1439,14 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F16" s="24" t="s">
+      <c r="F16" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="18">
         <v>0.1</v>
       </c>
       <c r="H16" s="5"/>
-      <c r="I16" s="5">
+      <c r="I16" s="61">
         <f t="shared" ref="I16:I20" si="5">+G16*H16</f>
         <v>0</v>
       </c>
@@ -1318,25 +1456,25 @@
       <c r="N16" s="2"/>
     </row>
     <row r="17" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="58">
         <v>0.2</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="4">
+      <c r="C17" s="59"/>
+      <c r="D17" s="51">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F17" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="14">
         <v>0.1</v>
       </c>
       <c r="H17" s="5"/>
-      <c r="I17" s="5">
+      <c r="I17" s="61">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -1352,40 +1490,40 @@
         <f>SUM(D13:D17)</f>
         <v>4.4990000000000006</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F18" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="14">
         <v>0.1</v>
       </c>
       <c r="H18" s="11"/>
-      <c r="I18" s="5">
+      <c r="I18" s="61">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="F19" s="16" t="s">
+      <c r="F19" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="14">
         <v>0.15</v>
       </c>
       <c r="H19" s="11"/>
-      <c r="I19" s="5">
+      <c r="I19" s="61">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="F20" s="35" t="s">
+    <row r="20" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F20" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="36">
+      <c r="G20" s="63">
         <v>0.2</v>
       </c>
-      <c r="H20" s="11"/>
-      <c r="I20" s="5">
+      <c r="H20" s="50"/>
+      <c r="I20" s="64">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
@@ -1403,7 +1541,7 @@
       <c r="H21" s="1"/>
       <c r="I21" s="12">
         <f>SUM(I13:I20)</f>
-        <v>1.335</v>
+        <v>2.2444999999999999</v>
       </c>
       <c r="K21"/>
       <c r="L21"/>

--- a/Ciclo 02 - 2026/Cuadro de notas.xlsx
+++ b/Ciclo 02 - 2026/Cuadro de notas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luizi\OneDrive\Escritorio\UES-2026\Ciclo 02 - 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis Vasquez\Desktop\UES-2026\Ciclo 02 - 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46FD267F-17D8-4C33-8E39-974C4072CEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F03A8D-374E-417E-A34E-72897259A5DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{8B416A22-FD13-409B-B356-C908504C11D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -624,51 +627,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
@@ -704,6 +662,51 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1020,36 +1023,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A82A0CD-7BCC-4D99-8D34-01F85165CA32}">
   <dimension ref="A1:N21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="33"/>
-      <c r="F2" s="34" t="s">
+    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="58"/>
+      <c r="F2" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="36"/>
-      <c r="K2" s="37" t="s">
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="I2" s="61"/>
+      <c r="K2" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="39"/>
-    </row>
-    <row r="3" spans="1:14" s="2" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="40" t="s">
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="64"/>
+    </row>
+    <row r="3" spans="1:14" s="2" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="25" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="17">
@@ -1062,7 +1065,7 @@
         <f>+C3*B3</f>
         <v>1.5</v>
       </c>
-      <c r="F3" s="40" t="s">
+      <c r="F3" s="25" t="s">
         <v>21</v>
       </c>
       <c r="G3" s="17">
@@ -1075,7 +1078,7 @@
         <f>+G3*H3</f>
         <v>1</v>
       </c>
-      <c r="K3" s="52" t="s">
+      <c r="K3" s="37" t="s">
         <v>26</v>
       </c>
       <c r="L3" s="18">
@@ -1089,8 +1092,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="41" t="s">
+    <row r="4" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="26" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="23">
@@ -1103,7 +1106,7 @@
         <f t="shared" ref="D4:D8" si="0">+C4*B4</f>
         <v>0.81400000000000006</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="26" t="s">
         <v>22</v>
       </c>
       <c r="G4" s="23">
@@ -1116,7 +1119,7 @@
         <f t="shared" ref="I4:I8" si="1">+G4*H4</f>
         <v>1.1399999999999999</v>
       </c>
-      <c r="K4" s="47" t="s">
+      <c r="K4" s="32" t="s">
         <v>6</v>
       </c>
       <c r="L4" s="16">
@@ -1130,8 +1133,8 @@
         <v>1.0725</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="40" t="s">
+    <row r="5" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="25" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="17">
@@ -1144,7 +1147,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F5" s="47" t="s">
+      <c r="F5" s="32" t="s">
         <v>23</v>
       </c>
       <c r="G5" s="16">
@@ -1157,7 +1160,7 @@
         <f t="shared" si="1"/>
         <v>1.47</v>
       </c>
-      <c r="K5" s="40" t="s">
+      <c r="K5" s="25" t="s">
         <v>27</v>
       </c>
       <c r="L5" s="17">
@@ -1171,8 +1174,8 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="42" t="s">
+    <row r="6" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="27" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="14">
@@ -1183,7 +1186,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F6" s="48" t="s">
+      <c r="F6" s="33" t="s">
         <v>24</v>
       </c>
       <c r="G6" s="20">
@@ -1194,7 +1197,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K6" s="49" t="s">
+      <c r="K6" s="34" t="s">
         <v>28</v>
       </c>
       <c r="L6" s="19">
@@ -1206,8 +1209,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="43" t="s">
+    <row r="7" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="28" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="15">
@@ -1218,7 +1221,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F7" s="49" t="s">
+      <c r="F7" s="34" t="s">
         <v>25</v>
       </c>
       <c r="G7" s="19">
@@ -1229,7 +1232,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K7" s="49" t="s">
+      <c r="K7" s="34" t="s">
         <v>29</v>
       </c>
       <c r="L7" s="19">
@@ -1241,30 +1244,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="44" t="s">
+    <row r="8" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="29" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="13">
         <v>0.2</v>
       </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="46">
+      <c r="C8" s="30"/>
+      <c r="D8" s="31">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F8" s="49" t="s">
+      <c r="F8" s="34" t="s">
         <v>6</v>
       </c>
       <c r="G8" s="19">
         <v>0.2</v>
       </c>
-      <c r="H8" s="50"/>
-      <c r="I8" s="51">
+      <c r="H8" s="35"/>
+      <c r="I8" s="36">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K8" s="53" t="s">
+      <c r="K8" s="38" t="s">
         <v>8</v>
       </c>
       <c r="L8" s="21">
@@ -1276,7 +1279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B9" s="9">
         <f>SUM(B3:B8)</f>
         <v>1</v>
@@ -1294,34 +1297,34 @@
         <f>SUM(I3:I8)</f>
         <v>3.6099999999999994</v>
       </c>
-      <c r="K9" s="49" t="s">
+      <c r="K9" s="34" t="s">
         <v>20</v>
       </c>
       <c r="L9" s="19">
         <v>0.2</v>
       </c>
-      <c r="M9" s="54"/>
+      <c r="M9" s="39"/>
       <c r="N9" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="K10" s="49" t="s">
+      <c r="K10" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="L10" s="55">
+      <c r="L10" s="40">
         <v>0.1</v>
       </c>
-      <c r="M10" s="56"/>
-      <c r="N10" s="51">
+      <c r="M10" s="41"/>
+      <c r="N10" s="36">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="L11" s="1">
@@ -1333,22 +1336,22 @@
         <v>2.9724999999999997</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="25" t="s">
+    <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="27"/>
-      <c r="F12" s="28" t="s">
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="52"/>
+      <c r="F12" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="30"/>
-    </row>
-    <row r="13" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="52" t="s">
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="55"/>
+    </row>
+    <row r="13" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="37" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="18">
@@ -1361,7 +1364,7 @@
         <f>+B13*C13</f>
         <v>2</v>
       </c>
-      <c r="F13" s="40" t="s">
+      <c r="F13" s="25" t="s">
         <v>15</v>
       </c>
       <c r="G13" s="17">
@@ -1370,37 +1373,39 @@
       <c r="H13" s="3">
         <v>8.6</v>
       </c>
-      <c r="I13" s="60">
+      <c r="I13" s="45">
         <f t="shared" ref="I13:I14" si="3">+G13*H13</f>
         <v>0.86</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
+    <row r="14" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="32" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="16">
         <v>0.15</v>
       </c>
-      <c r="C14" s="5"/>
+      <c r="C14" s="5">
+        <v>9.3000000000000007</v>
+      </c>
       <c r="D14" s="24">
         <f t="shared" ref="D14:D17" si="4">+B14*C14</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="52" t="s">
+        <v>1.395</v>
+      </c>
+      <c r="F14" s="37" t="s">
         <v>16</v>
       </c>
       <c r="G14" s="18">
         <v>0.1</v>
       </c>
       <c r="H14" s="5"/>
-      <c r="I14" s="61">
+      <c r="I14" s="46">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="47" t="s">
+    <row r="15" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="32" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="16">
@@ -1413,7 +1418,7 @@
         <f t="shared" si="4"/>
         <v>2.4990000000000001</v>
       </c>
-      <c r="F15" s="40" t="s">
+      <c r="F15" s="25" t="s">
         <v>6</v>
       </c>
       <c r="G15" s="17">
@@ -1422,13 +1427,13 @@
       <c r="H15" s="5">
         <v>9.23</v>
       </c>
-      <c r="I15" s="61">
+      <c r="I15" s="46">
         <f>+G15*H15</f>
         <v>1.3845000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="44" t="s">
+    <row r="16" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="29" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="13">
@@ -1439,14 +1444,14 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F16" s="52" t="s">
+      <c r="F16" s="37" t="s">
         <v>17</v>
       </c>
       <c r="G16" s="18">
         <v>0.1</v>
       </c>
       <c r="H16" s="5"/>
-      <c r="I16" s="61">
+      <c r="I16" s="46">
         <f t="shared" ref="I16:I20" si="5">+G16*H16</f>
         <v>0</v>
       </c>
@@ -1455,31 +1460,31 @@
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
     </row>
-    <row r="17" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="57" t="s">
+    <row r="17" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="58">
+      <c r="B17" s="43">
         <v>0.2</v>
       </c>
-      <c r="C17" s="59"/>
-      <c r="D17" s="51">
+      <c r="C17" s="44"/>
+      <c r="D17" s="36">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="F17" s="42" t="s">
+      <c r="F17" s="27" t="s">
         <v>18</v>
       </c>
       <c r="G17" s="14">
         <v>0.1</v>
       </c>
       <c r="H17" s="5"/>
-      <c r="I17" s="61">
+      <c r="I17" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="7"/>
       <c r="B18" s="9">
         <f>SUM(B13:B17)</f>
@@ -1488,47 +1493,47 @@
       <c r="C18" s="8"/>
       <c r="D18" s="12">
         <f>SUM(D13:D17)</f>
-        <v>4.4990000000000006</v>
-      </c>
-      <c r="F18" s="42" t="s">
+        <v>5.8940000000000001</v>
+      </c>
+      <c r="F18" s="27" t="s">
         <v>19</v>
       </c>
       <c r="G18" s="14">
         <v>0.1</v>
       </c>
       <c r="H18" s="11"/>
-      <c r="I18" s="61">
+      <c r="I18" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="F19" s="42" t="s">
+    <row r="19" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="F19" s="27" t="s">
         <v>8</v>
       </c>
       <c r="G19" s="14">
         <v>0.15</v>
       </c>
       <c r="H19" s="11"/>
-      <c r="I19" s="61">
+      <c r="I19" s="46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F20" s="62" t="s">
+    <row r="20" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F20" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="G20" s="63">
+      <c r="G20" s="48">
         <v>0.2</v>
       </c>
-      <c r="H20" s="50"/>
-      <c r="I20" s="64">
+      <c r="H20" s="35"/>
+      <c r="I20" s="49">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14" s="2" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" s="2" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A21"/>
       <c r="B21"/>
       <c r="C21"/>
